--- a/ksoft/docs/records/Item_Unit_Measure_Records.xlsx
+++ b/ksoft/docs/records/Item_Unit_Measure_Records.xlsx
@@ -1601,13 +1601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522DA00C-1D21-418D-8DC3-54A2FAFBA488}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07C5E081-9CF2-4BD6-849B-104E7877948A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECE64BB-9671-4DA8-8BBF-2C428BE2F050}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F77E81F7-B2C3-48BE-AD49-CD4E01A775FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899959F5-5869-4276-A5AA-F913A74967B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE4800DB-543E-4AB6-9ADC-6B0C04A4CF72}"/>
 </file>
--- a/ksoft/docs/records/Item_Unit_Measure_Records.xlsx
+++ b/ksoft/docs/records/Item_Unit_Measure_Records.xlsx
@@ -1601,13 +1601,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07C5E081-9CF2-4BD6-849B-104E7877948A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{522DA00C-1D21-418D-8DC3-54A2FAFBA488}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F77E81F7-B2C3-48BE-AD49-CD4E01A775FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ECE64BB-9671-4DA8-8BBF-2C428BE2F050}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE4800DB-543E-4AB6-9ADC-6B0C04A4CF72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899959F5-5869-4276-A5AA-F913A74967B5}"/>
 </file>